--- a/results/04_feature_selection/04d_ALL_consensus_nested.xlsx
+++ b/results/04_feature_selection/04d_ALL_consensus_nested.xlsx
@@ -516,7 +516,7 @@
         <v>77.5</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5986304819496672</v>
+        <v>0.6387926515082863</v>
       </c>
       <c r="G2" t="n">
         <v>0.2769115477721268</v>
@@ -557,7 +557,7 @@
         <v>78.04878048780488</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5608463965702838</v>
+        <v>0.6064131946658647</v>
       </c>
       <c r="G3" t="n">
         <v>0.295146051008736</v>
@@ -587,7 +587,7 @@
         <v>42</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>85.71428571428572</v>
+        <v>88.09523809523809</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4656727639764346</v>
+        <v>0.4692218250748227</v>
       </c>
       <c r="G4" t="n">
         <v>0.4193757988861722</v>
@@ -607,10 +607,10 @@
         <v>0.7317904491106442</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7416451769600094</v>
+        <v>0.7371297104138026</v>
       </c>
       <c r="J4" t="n">
-        <v>101.3466598069628</v>
+        <v>100.7296161503129</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
         <v>43</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -636,10 +636,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>81.3953488372093</v>
+        <v>83.72093023255813</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5630069537086833</v>
+        <v>0.5876632501947429</v>
       </c>
       <c r="G5" t="n">
         <v>0.322242066632012</v>
@@ -648,10 +648,10 @@
         <v>0.7584511382732912</v>
       </c>
       <c r="I5" t="n">
-        <v>0.740204074741885</v>
+        <v>0.7423180768872754</v>
       </c>
       <c r="J5" t="n">
-        <v>97.5941675593041</v>
+        <v>97.87289377365234</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         <v>41</v>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>75.60975609756098</v>
+        <v>78.04878048780488</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5834959201018142</v>
+        <v>0.6050546722159541</v>
       </c>
       <c r="G6" t="n">
         <v>0.3803651501032307</v>
@@ -689,10 +689,10 @@
         <v>0.8468093876883849</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8380082807867801</v>
+        <v>0.8384060741259433</v>
       </c>
       <c r="J6" t="n">
-        <v>98.96067438203183</v>
+        <v>99.00764992870698</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -744,50 +744,50 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Random_Forest</t>
+          <t>Elastic_Net</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.8604651162790697</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="D2" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Spearman</t>
+          <t>Lasso_L1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mutual_Info</t>
+          <t>Random_Forest</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.8125</v>
+        <v>0.8604651162790697</v>
       </c>
       <c r="D3" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Spearman</t>
+          <t>Elastic_Net</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ANOVA_F</t>
+          <t>Random_Forest</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.6774193548387096</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D4" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5">
@@ -798,29 +798,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lasso_L1</t>
+          <t>Mutual_Info</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.6511627906976745</v>
+        <v>0.8125</v>
       </c>
       <c r="D5" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mutual_Info</t>
+          <t>Elastic_Net</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lasso_L1</t>
+          <t>Ridge_L2</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.6511627906976745</v>
+        <v>0.7</v>
       </c>
       <c r="D6" t="n">
         <v>28</v>
@@ -829,25 +829,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Spearman</t>
+          <t>Lasso_L1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Random_Forest</t>
+          <t>Ridge_L2</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.6341463414634146</v>
+        <v>0.6904761904761905</v>
       </c>
       <c r="D7" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Mutual_Info</t>
+          <t>Spearman</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -856,136 +856,136 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.5757575757575758</v>
+        <v>0.6774193548387096</v>
       </c>
       <c r="D8" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mutual_Info</t>
+          <t>Spearman</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Random_Forest</t>
+          <t>Lasso_L1</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.5581395348837209</v>
+        <v>0.6511627906976745</v>
       </c>
       <c r="D9" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ANOVA_F</t>
+          <t>Mutual_Info</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Random_Forest</t>
+          <t>Lasso_L1</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.525</v>
+        <v>0.6511627906976745</v>
       </c>
       <c r="D10" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ANOVA_F</t>
+          <t>Spearman</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Lasso_L1</t>
+          <t>Random_Forest</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.5116279069767442</v>
+        <v>0.6341463414634146</v>
       </c>
       <c r="D11" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>RFECV</t>
+          <t>Mutual_Info</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lasso_L1</t>
+          <t>Elastic_Net</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.4523809523809524</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="D12" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Spearman</t>
+          <t>RFECV</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>RFECV</t>
+          <t>Ridge_L2</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.4117647058823529</v>
+        <v>0.6</v>
       </c>
       <c r="D13" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ANOVA_F</t>
+          <t>Ridge_L2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>RFECV</t>
+          <t>Random_Forest</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.4</v>
+        <v>0.5952380952380952</v>
       </c>
       <c r="D14" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RFECV</t>
+          <t>Spearman</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Random_Forest</t>
+          <t>Elastic_Net</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.3902439024390244</v>
+        <v>0.5813953488372093</v>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16">
@@ -996,13 +996,247 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>ANOVA_F</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0.5757575757575758</v>
+      </c>
+      <c r="D16" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Mutual_Info</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Random_Forest</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.5581395348837209</v>
+      </c>
+      <c r="D17" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Spearman</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ridge_L2</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.5263157894736842</v>
+      </c>
+      <c r="D18" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ANOVA_F</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Random_Forest</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="D19" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ANOVA_F</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Elastic_Net</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.5121951219512195</v>
+      </c>
+      <c r="D20" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ANOVA_F</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Lasso_L1</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0.5116279069767442</v>
+      </c>
+      <c r="D21" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Mutual_Info</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ridge_L2</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0.4871794871794872</v>
+      </c>
+      <c r="D22" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ANOVA_F</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ridge_L2</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0.4857142857142857</v>
+      </c>
+      <c r="D23" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>RFECV</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Lasso_L1</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.4523809523809524</v>
+      </c>
+      <c r="D24" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>RFECV</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Elastic_Net</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D25" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Spearman</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>RFECV</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.4117647058823529</v>
+      </c>
+      <c r="D26" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ANOVA_F</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>RFECV</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D27" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>RFECV</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Random_Forest</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.3902439024390244</v>
+      </c>
+      <c r="D28" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Mutual_Info</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>RFECV</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D29" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1017,7 +1251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1063,37 +1297,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Mutual_Info</t>
+          <t>Lasso_L1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ANOVA_F</t>
+          <t>Elastic_Net</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.7575757575757576</v>
+        <v>0.84375</v>
       </c>
       <c r="D3" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Spearman</t>
+          <t>Elastic_Net</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ANOVA_F</t>
+          <t>Ridge_L2</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.7058823529411765</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
@@ -1104,11 +1338,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Random_Forest</t>
+          <t>Ridge_L2</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.6341463414634146</v>
+        <v>0.8125</v>
       </c>
       <c r="D5" t="n">
         <v>26</v>
@@ -1122,14 +1356,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lasso_L1</t>
+          <t>ANOVA_F</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.6216216216216216</v>
+        <v>0.7575757575757576</v>
       </c>
       <c r="D6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
@@ -1140,11 +1374,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Random_Forest</t>
+          <t>ANOVA_F</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.5853658536585366</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="D7" t="n">
         <v>24</v>
@@ -1158,20 +1392,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Random_Forest</t>
+          <t>Ridge_L2</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.5853658536585366</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="D8" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ANOVA_F</t>
+          <t>Lasso_L1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1180,34 +1414,34 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.5853658536585366</v>
+        <v>0.6341463414634146</v>
       </c>
       <c r="D9" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Spearman</t>
+          <t>RFECV</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lasso_L1</t>
+          <t>Ridge_L2</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.6296296296296297</v>
       </c>
       <c r="D10" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ANOVA_F</t>
+          <t>Mutual_Info</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1216,28 +1450,28 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.6216216216216216</v>
       </c>
       <c r="D11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>RFECV</t>
+          <t>Elastic_Net</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lasso_L1</t>
+          <t>Random_Forest</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.5483870967741935</v>
+        <v>0.6</v>
       </c>
       <c r="D12" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13">
@@ -1248,67 +1482,301 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>RFECV</t>
+          <t>Ridge_L2</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.4375</v>
+        <v>0.6</v>
       </c>
       <c r="D13" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Mutual_Info</t>
+          <t>ANOVA_F</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>RFECV</t>
+          <t>Random_Forest</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.4375</v>
+        <v>0.5853658536585366</v>
       </c>
       <c r="D14" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ANOVA_F</t>
+          <t>Spearman</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RFECV</t>
+          <t>Random_Forest</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.4375</v>
+        <v>0.5853658536585366</v>
       </c>
       <c r="D15" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>Mutual_Info</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Random_Forest</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0.5853658536585366</v>
+      </c>
+      <c r="D16" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ANOVA_F</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Lasso_L1</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.5789473684210527</v>
+      </c>
+      <c r="D17" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Spearman</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Lasso_L1</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.5789473684210527</v>
+      </c>
+      <c r="D18" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Ridge_L2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Random_Forest</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="D19" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ANOVA_F</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ridge_L2</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="D20" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>RFECV</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Elastic_Net</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0.5517241379310345</v>
+      </c>
+      <c r="D21" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>RFECV</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Lasso_L1</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0.5483870967741935</v>
+      </c>
+      <c r="D22" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Mutual_Info</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Elastic_Net</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0.5405405405405406</v>
+      </c>
+      <c r="D23" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ANOVA_F</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Elastic_Net</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D24" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Spearman</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Elastic_Net</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D25" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ANOVA_F</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>RFECV</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="D26" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Mutual_Info</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>RFECV</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="D27" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Spearman</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>RFECV</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="D28" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>RFECV</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
         <is>
           <t>Random_Forest</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C29" t="n">
         <v>0.325</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D29" t="n">
         <v>13</v>
       </c>
     </row>
@@ -1323,7 +1791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1421,13 +1889,43 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Random_Forest</t>
+          <t>Elastic_Net</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>40</v>
       </c>
       <c r="C7" t="inlineStr">
+        <is>
+          <t>A1, A2, A3, A5, A6, A9, A12, A13, A15, A17...</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ridge_L2</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>28</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>A12, A28, A60, A15, A45, A2, A41, A36, A3, A21...</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Random_Forest</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>40</v>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>A1, A2, A3, A5, A6, A9, A12, A13, A15, A17...</t>
         </is>
@@ -1444,7 +1942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1542,13 +2040,43 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Elastic_Net</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>40</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>A1, A2, A3, A5, A6, A9, A12, A15, A17, A20...</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ridge_L2</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>29</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>A2, A21, A62, A6, A20, A31, A60, A56, A29, A41...</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Random_Forest</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B9" t="n">
         <v>41</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>A1, A2, A3, A5, A6, A9, A12, A15, A17, A20...</t>
         </is>
@@ -1565,7 +2093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1663,13 +2191,43 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Elastic_Net</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>18</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>A13, A15, A20, A21, A24, A25, A26, A34, A35, A36...</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ridge_L2</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>30</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>A58, A17, A64, A34, A53, A15, A41, A2, A11, A3...</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Random_Forest</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B9" t="n">
         <v>42</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>A2, A3, A5, A6, A9, A11, A12, A13, A15, A17...</t>
         </is>
@@ -1686,7 +2244,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1784,13 +2342,43 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Elastic_Net</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>39</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>A1, A2, A3, A5, A6, A9, A13, A15, A17, A20...</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ridge_L2</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>29</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>A24, A5, A3, A6, A59, A64, A41, A35, A30, A53...</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Random_Forest</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B9" t="n">
         <v>38</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>A2, A3, A5, A6, A9, A12, A13, A17, A20, A21...</t>
         </is>
@@ -1807,7 +2395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1905,13 +2493,43 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Elastic_Net</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>28</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>A1, A3, A20, A21, A24, A25, A26, A27, A29, A34...</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ridge_L2</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>27</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>A55, A37, A27, A12, A42, A58, A44, A57, A30, A40...</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Random_Forest</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B9" t="n">
         <v>36</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>A3, A5, A6, A9, A12, A15, A17, A20, A21, A24...</t>
         </is>
@@ -1928,7 +2546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1956,7 +2574,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Lasso_L1</t>
+          <t>Elastic_Net</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1965,46 +2583,46 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Spearman</t>
+          <t>Lasso_L1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mutual_Info</t>
+          <t>Random_Forest</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.7575757575757576</v>
+        <v>0.9</v>
       </c>
       <c r="D3" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Spearman</t>
+          <t>Lasso_L1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ANOVA_F</t>
+          <t>Elastic_Net</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.9</v>
       </c>
       <c r="D4" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
@@ -2015,92 +2633,92 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Random_Forest</t>
+          <t>Mutual_Info</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.725</v>
+        <v>0.7575757575757576</v>
       </c>
       <c r="D5" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mutual_Info</t>
+          <t>Spearman</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Random_Forest</t>
+          <t>ANOVA_F</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.725</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="D6" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mutual_Info</t>
+          <t>Spearman</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ANOVA_F</t>
+          <t>Ridge_L2</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.6774193548387096</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="D7" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Spearman</t>
+          <t>Mutual_Info</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Lasso_L1</t>
+          <t>Random_Forest</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.625</v>
+        <v>0.725</v>
       </c>
       <c r="D8" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mutual_Info</t>
+          <t>Spearman</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lasso_L1</t>
+          <t>Elastic_Net</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.625</v>
+        <v>0.725</v>
       </c>
       <c r="D9" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ANOVA_F</t>
+          <t>Spearman</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2109,117 +2727,351 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.575</v>
+        <v>0.725</v>
       </c>
       <c r="D10" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ANOVA_F</t>
+          <t>Mutual_Info</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Lasso_L1</t>
+          <t>Elastic_Net</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.5128205128205128</v>
+        <v>0.725</v>
       </c>
       <c r="D11" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Spearman</t>
+          <t>Elastic_Net</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RFECV</t>
+          <t>Ridge_L2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.4375</v>
+        <v>0.7</v>
       </c>
       <c r="D12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Mutual_Info</t>
+          <t>Ridge_L2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>RFECV</t>
+          <t>Random_Forest</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.4375</v>
+        <v>0.7</v>
       </c>
       <c r="D13" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>Mutual_Info</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>ANOVA_F</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>RFECV</t>
-        </is>
-      </c>
       <c r="C14" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.6774193548387096</v>
       </c>
       <c r="D14" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RFECV</t>
+          <t>Mutual_Info</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Random_Forest</t>
+          <t>Ridge_L2</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.425</v>
+        <v>0.6285714285714286</v>
       </c>
       <c r="D15" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>Mutual_Info</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Lasso_L1</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="D16" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Spearman</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Lasso_L1</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="D17" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>RFECV</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ridge_L2</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.6071428571428571</v>
+      </c>
+      <c r="D18" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Lasso_L1</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ridge_L2</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D19" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ANOVA_F</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ridge_L2</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.59375</v>
+      </c>
+      <c r="D20" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ANOVA_F</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Elastic_Net</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="D21" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ANOVA_F</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Random_Forest</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="D22" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ANOVA_F</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Lasso_L1</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0.5128205128205128</v>
+      </c>
+      <c r="D23" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Mutual_Info</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>RFECV</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="D24" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Spearman</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>RFECV</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="D25" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ANOVA_F</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>RFECV</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="D26" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>RFECV</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Elastic_Net</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="D27" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>RFECV</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Random_Forest</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="D28" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>RFECV</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Lasso_L1</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
         <v>0.3947368421052632</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D29" t="n">
         <v>15</v>
       </c>
     </row>
@@ -2234,7 +3086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2262,7 +3114,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Lasso_L1</t>
+          <t>Elastic_Net</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2271,70 +3123,70 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.926829268292683</v>
+        <v>0.975609756097561</v>
       </c>
       <c r="D2" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Spearman</t>
+          <t>Lasso_L1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ANOVA_F</t>
+          <t>Random_Forest</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.75</v>
+        <v>0.926829268292683</v>
       </c>
       <c r="D3" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Spearman</t>
+          <t>Lasso_L1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Random_Forest</t>
+          <t>Elastic_Net</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.6341463414634146</v>
+        <v>0.9024390243902439</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Spearman</t>
+          <t>Lasso_L1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mutual_Info</t>
+          <t>Ridge_L2</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="D5" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mutual_Info</t>
+          <t>Spearman</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2343,70 +3195,70 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.5862068965517241</v>
+        <v>0.75</v>
       </c>
       <c r="D6" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mutual_Info</t>
+          <t>Elastic_Net</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Lasso_L1</t>
+          <t>Ridge_L2</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.5641025641025641</v>
+        <v>0.725</v>
       </c>
       <c r="D7" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Spearman</t>
+          <t>Ridge_L2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Lasso_L1</t>
+          <t>Random_Forest</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.5609756097560976</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="D8" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mutual_Info</t>
+          <t>Spearman</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Random_Forest</t>
+          <t>Elastic_Net</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.5609756097560976</v>
+        <v>0.65</v>
       </c>
       <c r="D9" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ANOVA_F</t>
+          <t>Spearman</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2415,28 +3267,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.5609756097560976</v>
+        <v>0.6341463414634146</v>
       </c>
       <c r="D10" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ANOVA_F</t>
+          <t>Spearman</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Lasso_L1</t>
+          <t>Mutual_Info</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.525</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="D11" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
@@ -2447,14 +3299,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RFECV</t>
+          <t>Ridge_L2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.4814814814814815</v>
+        <v>0.625</v>
       </c>
       <c r="D12" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -2465,11 +3317,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lasso_L1</t>
+          <t>Ridge_L2</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.4473684210526316</v>
+        <v>0.5862068965517241</v>
       </c>
       <c r="D13" t="n">
         <v>17</v>
@@ -2478,54 +3330,288 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Spearman</t>
+          <t>Mutual_Info</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>RFECV</t>
+          <t>ANOVA_F</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.4333333333333333</v>
+        <v>0.5862068965517241</v>
       </c>
       <c r="D14" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RFECV</t>
+          <t>Mutual_Info</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Random_Forest</t>
+          <t>Elastic_Net</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.4146341463414634</v>
+        <v>0.575</v>
       </c>
       <c r="D15" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>ANOVA_F</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Elastic_Net</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="D16" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Spearman</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ridge_L2</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="D17" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>Mutual_Info</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Lasso_L1</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.5641025641025641</v>
+      </c>
+      <c r="D18" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Mutual_Info</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Random_Forest</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.5609756097560976</v>
+      </c>
+      <c r="D19" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Spearman</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Lasso_L1</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.5609756097560976</v>
+      </c>
+      <c r="D20" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ANOVA_F</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Random_Forest</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0.5609756097560976</v>
+      </c>
+      <c r="D21" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ANOVA_F</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Lasso_L1</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="D22" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Mutual_Info</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ridge_L2</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0.4857142857142857</v>
+      </c>
+      <c r="D23" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ANOVA_F</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
         <is>
           <t>RFECV</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C24" t="n">
+        <v>0.4814814814814815</v>
+      </c>
+      <c r="D24" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>RFECV</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Lasso_L1</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.4473684210526316</v>
+      </c>
+      <c r="D25" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Spearman</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>RFECV</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.4333333333333333</v>
+      </c>
+      <c r="D26" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>RFECV</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Elastic_Net</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="D27" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>RFECV</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Random_Forest</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.4146341463414634</v>
+      </c>
+      <c r="D28" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Mutual_Info</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>RFECV</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D29" t="n">
         <v>10</v>
       </c>
     </row>
@@ -2540,7 +3626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2586,30 +3672,30 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Spearman</t>
+          <t>Lasso_L1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mutual_Info</t>
+          <t>Elastic_Net</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.7741935483870968</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="D3" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Spearman</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Mutual_Info</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ANOVA_F</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -2627,20 +3713,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Random_Forest</t>
+          <t>ANOVA_F</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.6904761904761905</v>
+        <v>0.7741935483870968</v>
       </c>
       <c r="D5" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Spearman</t>
+          <t>Ridge_L2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2649,16 +3735,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.6190476190476191</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D6" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ANOVA_F</t>
+          <t>Mutual_Info</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2667,34 +3753,34 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.6190476190476191</v>
+        <v>0.6904761904761905</v>
       </c>
       <c r="D7" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RFECV</t>
+          <t>ANOVA_F</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Lasso_L1</t>
+          <t>Random_Forest</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Lasso_L1</t>
+          <t>Spearman</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2703,135 +3789,369 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.3809523809523809</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Spearman</t>
+          <t>Mutual_Info</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lasso_L1</t>
+          <t>Ridge_L2</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.3125</v>
+        <v>0.5945945945945946</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ANOVA_F</t>
+          <t>Elastic_Net</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Lasso_L1</t>
+          <t>Ridge_L2</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.3125</v>
+        <v>0.5483870967741935</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mutual_Info</t>
+          <t>Lasso_L1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lasso_L1</t>
+          <t>Ridge_L2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Mutual_Info</t>
+          <t>Spearman</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>RFECV</t>
+          <t>Ridge_L2</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.2580645161290323</v>
+        <v>0.5135135135135135</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Spearman</t>
+          <t>ANOVA_F</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>RFECV</t>
+          <t>Ridge_L2</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.2413793103448276</v>
+        <v>0.5135135135135135</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ANOVA_F</t>
+          <t>RFECV</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RFECV</t>
+          <t>Lasso_L1</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.2413793103448276</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>Elastic_Net</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Random_Forest</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="D16" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Lasso_L1</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Random_Forest</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="D17" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>RFECV</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Elastic_Net</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="D18" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Spearman</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Lasso_L1</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ANOVA_F</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Lasso_L1</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Mutual_Info</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Elastic_Net</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0.3055555555555556</v>
+      </c>
+      <c r="D21" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ANOVA_F</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Elastic_Net</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0.2941176470588235</v>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Spearman</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Elastic_Net</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0.2941176470588235</v>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>RFECV</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ridge_L2</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.2903225806451613</v>
+      </c>
+      <c r="D24" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Mutual_Info</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Lasso_L1</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Mutual_Info</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>RFECV</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.2580645161290323</v>
+      </c>
+      <c r="D26" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ANOVA_F</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>RFECV</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.2413793103448276</v>
+      </c>
+      <c r="D27" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Spearman</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>RFECV</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.2413793103448276</v>
+      </c>
+      <c r="D28" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>RFECV</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
         <is>
           <t>Random_Forest</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C29" t="n">
         <v>0.2380952380952381</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D29" t="n">
         <v>10</v>
       </c>
     </row>
